--- a/gc.xlsx
+++ b/gc.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student3\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student3\Documents\THE-InsectAttack\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0628D581-0120-41B3-9CBE-59986EB0EA15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C644477D-439D-41FD-B3BD-CCF1FB1C3762}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="90" yWindow="930" windowWidth="25830" windowHeight="13845" xr2:uid="{57A5F33F-DAB6-4E77-919B-5576544269BF}"/>
+    <workbookView xWindow="1515" yWindow="1110" windowWidth="21600" windowHeight="11295" xr2:uid="{57A5F33F-DAB6-4E77-919B-5576544269BF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1656,14 +1656,14 @@
         <v>25</v>
       </c>
       <c r="D8" s="13">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E8" s="10">
-        <v>46303</v>
+        <v>46315</v>
       </c>
       <c r="F8" s="10">
         <f>IF(E8="","",WORKDAY(E8,D8,祝日!$B$1:$B$16))</f>
-        <v>46314</v>
+        <v>46318</v>
       </c>
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
@@ -1768,11 +1768,11 @@
         <v>5</v>
       </c>
       <c r="E9" s="10">
-        <v>46313</v>
+        <v>46317</v>
       </c>
       <c r="F9" s="10">
         <f>IF(E9="","",WORKDAY(E9,D9,祝日!$B$1:$B$16))</f>
-        <v>46318</v>
+        <v>46324</v>
       </c>
       <c r="G9" s="4"/>
       <c r="H9" s="4"/>
@@ -1877,11 +1877,11 @@
         <v>7</v>
       </c>
       <c r="E10" s="10">
-        <v>46318</v>
+        <v>46324</v>
       </c>
       <c r="F10" s="10">
         <f>IF(E10="","",WORKDAY(E10,D10,祝日!$B$1:$B$16))</f>
-        <v>46329</v>
+        <v>46335</v>
       </c>
       <c r="G10" s="4"/>
       <c r="H10" s="4"/>
@@ -2313,11 +2313,11 @@
         <v>14</v>
       </c>
       <c r="E14" s="15">
-        <v>46310</v>
+        <v>46315</v>
       </c>
       <c r="F14" s="10">
         <f>IF(E14="","",WORKDAY(E14,D14,祝日!$B$1:$B$16))</f>
-        <v>46330</v>
+        <v>46335</v>
       </c>
       <c r="G14" s="4"/>
       <c r="H14" s="4"/>
@@ -3622,6 +3622,14 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="CF4:CL4"/>
+    <mergeCell ref="CM4:CS4"/>
+    <mergeCell ref="AP4:AV4"/>
+    <mergeCell ref="AW4:BC4"/>
+    <mergeCell ref="BD4:BJ4"/>
+    <mergeCell ref="BK4:BQ4"/>
+    <mergeCell ref="BR4:BX4"/>
+    <mergeCell ref="BY4:CE4"/>
     <mergeCell ref="AI4:AO4"/>
     <mergeCell ref="D4:D5"/>
     <mergeCell ref="B1:D2"/>
@@ -3633,14 +3641,6 @@
     <mergeCell ref="N4:T4"/>
     <mergeCell ref="U4:AA4"/>
     <mergeCell ref="AB4:AH4"/>
-    <mergeCell ref="CF4:CL4"/>
-    <mergeCell ref="CM4:CS4"/>
-    <mergeCell ref="AP4:AV4"/>
-    <mergeCell ref="AW4:BC4"/>
-    <mergeCell ref="BD4:BJ4"/>
-    <mergeCell ref="BK4:BQ4"/>
-    <mergeCell ref="BR4:BX4"/>
-    <mergeCell ref="BY4:CE4"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="G5:CS5">
